--- a/Collections/EURO/Italy/#EURO#Italy#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Italy/#EURO#Italy#Regular#[2002-present]#circulation_quality.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Italy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C49ADF-12C9-42B5-AEC9-0F7736C42F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D734BF-5759-4D29-BF15-0872D628E552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -388,7 +391,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="136">
   <si>
     <t>Year</t>
   </si>
@@ -787,6 +790,15 @@
   </si>
   <si>
     <t>Subtype_2#Map_of_Europe</t>
+  </si>
+  <si>
+    <t>19.000</t>
+  </si>
+  <si>
+    <t>15.500</t>
+  </si>
+  <si>
+    <t>200.000.000</t>
   </si>
 </sst>
 </file>
@@ -1098,15 +1110,14 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="51">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1292,6 +1303,207 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1323,9 +1535,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="49" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1594,7 +1806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2127,6 +2339,50 @@
         <v/>
       </c>
     </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" ref="G25:G26" si="3">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
@@ -2135,11 +2391,26 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="25" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="44" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2151,9 +2422,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="containsText" dxfId="43" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -2166,9 +2437,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+  <conditionalFormatting sqref="F21:F24">
+    <cfRule type="containsText" dxfId="42" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -2181,9 +2452,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F24">
-    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+  <conditionalFormatting sqref="F25:F26">
+    <cfRule type="containsText" dxfId="41" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -2204,7 +2475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2689,7 +2960,7 @@
         <v>110</v>
       </c>
       <c r="G22" s="3" t="str">
-        <f t="shared" ref="G22:G24" si="1">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G22:G26" si="1">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2733,6 +3004,50 @@
         <v>110</v>
       </c>
       <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2745,11 +3060,26 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="21" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="40" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2761,9 +3091,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="containsText" dxfId="38" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -2776,9 +3106,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+  <conditionalFormatting sqref="F21:F24">
+    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -2791,9 +3121,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F24">
-    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+  <conditionalFormatting sqref="F25:F26">
+    <cfRule type="containsText" dxfId="36" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -2814,7 +3144,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3299,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="str">
-        <f t="shared" ref="G22:G24" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G22:G26" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3343,6 +3673,50 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" ref="G25" si="3">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -3355,11 +3729,43 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20 F22 F24">
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F20 F22 F24">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21 F23">
+    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23 F21">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3371,12 +3777,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="32" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23">
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3396,7 +3802,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4055,6 +4461,56 @@
         <v/>
       </c>
     </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3" t="str">
+        <f>IF(OR(AND(G27&gt;1,G27&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H28" s="3" t="str">
+        <f t="shared" ref="H28" si="5">IF(OR(AND(G28&gt;1,G28&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <mergeCells count="2">
@@ -4063,12 +4519,12 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3 G6:G22 G24 G26">
-    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G22 G3 G24 G26">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -4080,12 +4536,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -4097,11 +4553,45 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23 G25">
+    <cfRule type="containsText" dxfId="28" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25 G23">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G27">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4113,12 +4603,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23 G25">
+  <conditionalFormatting sqref="G28">
     <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G23 G25">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4138,7 +4626,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4715,6 +5203,54 @@
         <v/>
       </c>
     </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f>IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" ref="G26" si="3">IF(OR(AND(F26&gt;1,F26&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <mergeCells count="2">
@@ -4723,11 +5259,45 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20 F22 F24">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F20 F22 F24">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21 F23">
+    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23 F21">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4739,12 +5309,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23">
+  <conditionalFormatting sqref="F26">
     <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4764,7 +5332,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5341,6 +5909,54 @@
         <v/>
       </c>
     </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f>IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" ref="G26" si="3">IF(OR(AND(F26&gt;1,F26&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <mergeCells count="2">
@@ -5349,11 +5965,45 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20 F22 F24">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F20 F22 F24">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21 F23">
+    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23 F21">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5365,12 +6015,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5390,7 +6038,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -6023,6 +6671,56 @@
         <v/>
       </c>
     </row>
+    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="12"/>
+      <c r="F26" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="str">
+        <f t="shared" ref="H26:H27" si="4">IF(OR(AND(G26&gt;1,G26&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H27" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
   <mergeCells count="2">
@@ -6031,11 +6729,43 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3 G5:G21 G23 G25">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G21 G3 G23 G25">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22 G24">
+    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24 G22">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6047,12 +6777,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22 G24">
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22 G24">
+  <conditionalFormatting sqref="G26">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6064,9 +6794,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+  <conditionalFormatting sqref="G27">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -6665,6 +7395,54 @@
         <v/>
       </c>
     </row>
+    <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" ref="G25:G26" si="3">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
     <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="Q29" s="26"/>
       <c r="R29" s="26"/>
@@ -6677,11 +7455,45 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20 F22 F24">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F20 F22 F24">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21 F23">
+    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23 F21">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6693,12 +7505,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>

--- a/Collections/EURO/Italy/#EURO#Italy#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Italy/#EURO#Italy#Regular#[2002-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Italy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D734BF-5759-4D29-BF15-0872D628E552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E697B1-AFCC-444C-8765-E0856624E479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -1110,14 +1110,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="40">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1415,95 +1416,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1535,9 +1447,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="49" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2391,7 +2303,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="45" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2408,7 +2320,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="44" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -2423,7 +2335,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="43" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -2438,7 +2350,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21:F24">
-    <cfRule type="containsText" dxfId="42" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -2453,7 +2365,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:F26">
-    <cfRule type="containsText" dxfId="41" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -2847,7 +2759,7 @@
         <v>47</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3060,7 +2972,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="40" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3077,7 +2989,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -3092,7 +3004,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="38" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -3107,7 +3019,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21:F24">
-    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -3122,7 +3034,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:F26">
-    <cfRule type="containsText" dxfId="36" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -3729,7 +3641,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20 F22 F24">
-    <cfRule type="containsText" dxfId="35" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3746,11 +3658,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21 F23">
-    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21">
+  <conditionalFormatting sqref="F21 F23">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3763,7 +3675,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -3778,7 +3690,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="containsText" dxfId="32" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4519,7 +4431,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3 G6:G22 G24 G26">
-    <cfRule type="containsText" dxfId="31" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4536,7 +4448,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="30" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4553,7 +4465,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="containsText" dxfId="29" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4570,11 +4482,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23 G25">
-    <cfRule type="containsText" dxfId="28" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G23))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25 G23">
+  <conditionalFormatting sqref="G23 G25">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4587,7 +4499,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4604,7 +4516,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G28))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -5259,7 +5171,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20 F22 F24">
-    <cfRule type="containsText" dxfId="27" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5276,11 +5188,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21 F23">
-    <cfRule type="containsText" dxfId="26" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21">
+  <conditionalFormatting sqref="F21 F23">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5293,7 +5205,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5310,7 +5222,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -5965,7 +5877,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20 F22 F24">
-    <cfRule type="containsText" dxfId="23" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5982,11 +5894,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21 F23">
-    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21">
+  <conditionalFormatting sqref="F21 F23">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5999,7 +5911,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6016,7 +5928,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -6729,7 +6641,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G3 G5:G21 G23 G25">
-    <cfRule type="containsText" dxfId="21" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6746,11 +6658,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G22 G24">
-    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G22))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G24 G22">
+  <conditionalFormatting sqref="G22 G24">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6763,7 +6675,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -6778,7 +6690,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G26))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6795,7 +6707,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G27))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -7455,7 +7367,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F20 F22 F24">
-    <cfRule type="containsText" dxfId="18" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7472,11 +7384,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21 F23">
-    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21">
+  <conditionalFormatting sqref="F21 F23">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7489,7 +7401,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7506,7 +7418,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
